--- a/backtest_runs/20260410_193731/by_symbol/AATM/AATM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AATM/AATM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
         <v>-6280.579999999999</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>100806.68</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>100806.68</v>
@@ -1231,7 +1231,7 @@
         <v>-950.7299999999951</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>103716.49</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>103716.49</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>103716.49</v>
@@ -1553,7 +1553,7 @@
         <v>-6395.819999999997</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>97320.67000000003</v>
